--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FRIVALCA LA MUELA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FRIVALCA LA MUELA.xlsx
@@ -565,13 +565,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>49.4047</v>
+        <v>30.8326</v>
       </c>
       <c r="E2" t="n">
-        <v>33.1229</v>
+        <v>21.8144</v>
       </c>
       <c r="F2" t="n">
-        <v>16.2818</v>
+        <v>9.0182</v>
       </c>
       <c r="G2" t="n">
         <v>14.8126</v>
@@ -610,13 +610,13 @@
         <v>44.9289</v>
       </c>
       <c r="S2" t="n">
-        <v>34.4246</v>
+        <v>15.8522</v>
       </c>
       <c r="T2" t="n">
-        <v>17.1453</v>
+        <v>5.836399999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>17.2794</v>
+        <v>10.0159</v>
       </c>
       <c r="V2" t="n">
         <v>18.3343</v>
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>12.3266</v>
+        <v>13.4542</v>
       </c>
       <c r="E3" t="n">
-        <v>4.683400000000001</v>
+        <v>1.9518</v>
       </c>
       <c r="F3" t="n">
-        <v>7.643300000000001</v>
+        <v>11.5025</v>
       </c>
       <c r="G3" t="n">
         <v>-2.3798</v>
@@ -688,13 +688,13 @@
         <v>23.8316</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0124</v>
+        <v>3.1401</v>
       </c>
       <c r="T3" t="n">
-        <v>5.8761</v>
+        <v>3.1443</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.864</v>
+        <v>-0.004699999999999982</v>
       </c>
       <c r="V3" t="n">
         <v>6.2478</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ABAD CALAVIA</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0494</v>
+        <v>5.6969</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0205</v>
+        <v>6.227500000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0698</v>
+        <v>-0.5305000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0494</v>
+        <v>-5.6996</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0494</v>
+        <v>-0.2115000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-5.4881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0205</v>
+        <v>5.7782</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0205</v>
+        <v>6.2687</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.4906999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0698</v>
+        <v>-11.4775</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0698</v>
+        <v>-6.4801</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-4.9974</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.0789</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-8.985899999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>14.0646</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.0318</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.1277</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.9040000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.285699999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>9.307099999999998</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-4.0214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LAFUENTE</t>
+          <t>D. ABAD CALAVIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,19 +799,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1842</v>
+        <v>-0.0494</v>
       </c>
       <c r="E5" t="n">
         <v>0.0205</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2047</v>
+        <v>-0.0698</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1842</v>
+        <v>-0.0494</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1842</v>
+        <v>-0.0494</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -826,10 +826,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2047</v>
+        <v>-0.0698</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2047</v>
+        <v>-0.0698</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>D. FERNANDEZ LAFUENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3857000000000017</v>
+        <v>-0.1842</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8197</v>
+        <v>0.0205</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2056</v>
+        <v>-0.2047</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.6996</v>
+        <v>-0.1842</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2115000000000001</v>
+        <v>-0.1842</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.4881</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7782</v>
+        <v>0.0205</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2687</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4906999999999999</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.4775</v>
+        <v>-0.2047</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.4801</v>
+        <v>-0.2047</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.9974</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.0789</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.985899999999999</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>14.0646</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.0509</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.28</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7708999999999999</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.285699999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>9.307099999999998</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.0214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5685</v>
+        <v>-0.413</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.508</v>
+        <v>-0.4535</v>
       </c>
       <c r="G7" t="n">
         <v>0.1998</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.159</v>
+        <v>-0.0034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6093</v>
@@ -1033,13 +1033,13 @@
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0521</v>
+        <v>-2.734900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.7442</v>
+        <v>-5.2098</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6919</v>
+        <v>2.4749</v>
       </c>
       <c r="G8" t="n">
         <v>0.6275999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>9.7669</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7996999999999999</v>
+        <v>-0.4824999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5829</v>
+        <v>1.117</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.3826</v>
+        <v>-1.5995</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2939</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.4</v>
+        <v>-6.6313</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.911</v>
+        <v>-9.3043</v>
       </c>
       <c r="F9" t="n">
-        <v>2.511</v>
+        <v>2.673</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9426</v>
@@ -1156,13 +1156,13 @@
         <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9999</v>
+        <v>-0.2311</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4525</v>
+        <v>-0.8459</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4527</v>
+        <v>0.6147</v>
       </c>
       <c r="V9" t="n">
         <v>0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>-11.3851</v>
+        <v>-7.5474</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1075</v>
+        <v>-0.8439999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.277700000000001</v>
+        <v>-6.7035</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5058</v>
@@ -1234,13 +1234,13 @@
         <v>8.009</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.906</v>
+        <v>0.9319999999999997</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2868</v>
+        <v>0.9768000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6191</v>
+        <v>-0.0450000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-7.5127</v>
@@ -1267,13 +1267,13 @@
         <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.2653</v>
+        <v>-7.6003</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8186</v>
+        <v>2.250100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.0836</v>
+        <v>-9.8505</v>
       </c>
       <c r="G11" t="n">
         <v>-5.902400000000001</v>
@@ -1312,13 +1312,13 @@
         <v>31.4503</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.122</v>
+        <v>-1.4572</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0084</v>
+        <v>1.4402</v>
       </c>
       <c r="U11" t="n">
-        <v>-8.1305</v>
+        <v>-2.8972</v>
       </c>
       <c r="V11" t="n">
         <v>-5.319599999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.2038</v>
+        <v>-9.7029</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.8779</v>
+        <v>-8.177</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3259</v>
+        <v>-1.526</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1539</v>
+        <v>-6.776300000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5932</v>
+        <v>-4.9673</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.5605</v>
+        <v>-1.809</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1602</v>
+        <v>0.3964</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5874</v>
+        <v>-2.52</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7477</v>
+        <v>2.9165</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.9935</v>
+        <v>-7.1726</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.1805</v>
+        <v>-2.4472</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8127999999999999</v>
+        <v>-4.7254</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.2975</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6973</v>
+        <v>-9.3764</v>
       </c>
       <c r="R12" t="n">
-        <v>8.399800000000001</v>
+        <v>8.008900000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5801999999999998</v>
+        <v>0.2351</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2386</v>
+        <v>0.2484</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3414000000000001</v>
+        <v>-0.01319999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1722</v>
+        <v>-1.7944</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0.5544</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.3908</v>
+        <v>-2.3489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.4027</v>
+        <v>-12.9786</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.4415</v>
+        <v>-12.2917</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.961000000000001</v>
+        <v>-0.6864999999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.776300000000001</v>
+        <v>-6.1539</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.9673</v>
+        <v>-2.5932</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.809</v>
+        <v>-3.5605</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3964</v>
+        <v>-1.1602</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.52</v>
+        <v>1.5874</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9165</v>
+        <v>-2.7477</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.1726</v>
+        <v>-4.9935</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.4472</v>
+        <v>-4.1805</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.7254</v>
+        <v>-0.8127999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3674</v>
+        <v>-4.2975</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.3764</v>
+        <v>-12.6973</v>
       </c>
       <c r="R13" t="n">
-        <v>8.008900000000001</v>
+        <v>8.399800000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.4647</v>
+        <v>-0.355</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.016</v>
+        <v>0.3472999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4486</v>
+        <v>-0.7023000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7944</v>
+        <v>-2.1722</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5544</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3489</v>
+        <v>-3.3908</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.7923</v>
+        <v>-22.1823</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.9931</v>
+        <v>-21.2495</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7991</v>
+        <v>-0.9330000000000003</v>
       </c>
       <c r="G14" t="n">
         <v>-15.1394</v>
@@ -1546,13 +1546,13 @@
         <v>9.181100000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7442</v>
+        <v>2.3541</v>
       </c>
       <c r="T14" t="n">
-        <v>5.0826</v>
+        <v>1.8266</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3385</v>
+        <v>0.5274000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1225</v>
@@ -1579,13 +1579,13 @@
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-25.6179</v>
+        <v>-26.4557</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.6886</v>
+        <v>-25.3772</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0706</v>
+        <v>-1.0781</v>
       </c>
       <c r="G15" t="n">
         <v>-18.648</v>
@@ -1624,13 +1624,13 @@
         <v>42.5849</v>
       </c>
       <c r="S15" t="n">
-        <v>5.7887</v>
+        <v>4.9504</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.343</v>
+        <v>0.9682999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>6.1309</v>
+        <v>3.9825</v>
       </c>
       <c r="V15" t="n">
         <v>24.5522</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.8636</v>
+        <v>-27.4541</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.2708</v>
+        <v>-28.812</v>
       </c>
       <c r="F16" t="n">
-        <v>-19.5931</v>
+        <v>1.3581</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.6175</v>
+        <v>-10.6708</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7499000000000007</v>
+        <v>-3.588000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.867599999999999</v>
+        <v>-7.083200000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>16.7067</v>
+        <v>4.004700000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>13.6578</v>
+        <v>5.949000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0488</v>
+        <v>-1.9442</v>
       </c>
       <c r="M16" t="n">
-        <v>-23.3243</v>
+        <v>-14.6757</v>
       </c>
       <c r="N16" t="n">
-        <v>-14.4076</v>
+        <v>-9.536799999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.916399999999999</v>
+        <v>-5.1389</v>
       </c>
       <c r="P16" t="n">
-        <v>-6.2511</v>
+        <v>-7.618399999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-31.4499</v>
+        <v>-38.2869</v>
       </c>
       <c r="R16" t="n">
-        <v>25.199</v>
+        <v>30.6687</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3601</v>
+        <v>1.5929</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9267000000000001</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4333</v>
+        <v>2.4989</v>
       </c>
       <c r="V16" t="n">
-        <v>-19.3553</v>
+        <v>-10.7575</v>
       </c>
       <c r="W16" t="n">
-        <v>3.545999999999999</v>
+        <v>6.3764</v>
       </c>
       <c r="X16" t="n">
-        <v>-22.9014</v>
+        <v>-17.1339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-32.7793</v>
+        <v>-28.7512</v>
       </c>
       <c r="E17" t="n">
-        <v>-31.3185</v>
+        <v>-9.280800000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4608</v>
+        <v>-19.4705</v>
       </c>
       <c r="G17" t="n">
-        <v>-10.6708</v>
+        <v>-6.6175</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.588000000000001</v>
+        <v>-0.7499000000000007</v>
       </c>
       <c r="I17" t="n">
-        <v>-7.083200000000001</v>
+        <v>-5.867599999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>4.004700000000001</v>
+        <v>16.7067</v>
       </c>
       <c r="K17" t="n">
-        <v>5.949000000000001</v>
+        <v>13.6578</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9442</v>
+        <v>3.0488</v>
       </c>
       <c r="M17" t="n">
-        <v>-14.6757</v>
+        <v>-23.3243</v>
       </c>
       <c r="N17" t="n">
-        <v>-9.536799999999999</v>
+        <v>-14.4076</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.1389</v>
+        <v>-8.916399999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.618399999999999</v>
+        <v>-6.2511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-38.2869</v>
+        <v>-31.4499</v>
       </c>
       <c r="R17" t="n">
-        <v>30.6687</v>
+        <v>25.199</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.7324</v>
+        <v>3.4727</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.4122</v>
+        <v>1.9163</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3201000000000001</v>
+        <v>1.5561</v>
       </c>
       <c r="V17" t="n">
-        <v>-10.7575</v>
+        <v>-19.3553</v>
       </c>
       <c r="W17" t="n">
-        <v>6.3764</v>
+        <v>3.545999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-17.1339</v>
+        <v>-22.9014</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-36.0018</v>
+        <v>-31.4624</v>
       </c>
       <c r="E18" t="n">
-        <v>-24.9466</v>
+        <v>-22.4398</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.0556</v>
+        <v>-9.022399999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-12.1342</v>
@@ -1858,13 +1858,13 @@
         <v>15.0413</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.3155</v>
+        <v>-0.7758999999999998</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.8754</v>
+        <v>-1.369</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4399</v>
+        <v>0.5931</v>
       </c>
       <c r="V18" t="n">
         <v>-9.3712</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.8061</v>
+        <v>-33.9571</v>
       </c>
       <c r="E19" t="n">
-        <v>-21.2538</v>
+        <v>-19.6799</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.5524</v>
+        <v>-14.2771</v>
       </c>
       <c r="G19" t="n">
         <v>-29.7877</v>
@@ -1936,13 +1936,13 @@
         <v>44.5381</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.2789</v>
+        <v>-0.4300000000000003</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3636</v>
+        <v>0.2106999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.9154</v>
+        <v>-0.6408999999999997</v>
       </c>
       <c r="V19" t="n">
         <v>4.660699999999999</v>
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-53.678</v>
+        <v>-38.0958</v>
       </c>
       <c r="E20" t="n">
-        <v>-46.379</v>
+        <v>-36.5746</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.299000000000001</v>
+        <v>-1.521</v>
       </c>
       <c r="G20" t="n">
         <v>6.188700000000001</v>
@@ -2014,13 +2014,13 @@
         <v>48.445</v>
       </c>
       <c r="S20" t="n">
-        <v>-15.3666</v>
+        <v>0.216</v>
       </c>
       <c r="T20" t="n">
-        <v>-11.2355</v>
+        <v>-1.4312</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.1312</v>
+        <v>1.6471</v>
       </c>
       <c r="V20" t="n">
         <v>-17.1526</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-237.7045</v>
+        <v>-206.2169</v>
       </c>
       <c r="E21" t="n">
-        <v>-177.5074</v>
+        <v>-166.9152</v>
       </c>
       <c r="F21" t="n">
-        <v>-60.1977</v>
+        <v>-39.3004</v>
       </c>
       <c r="G21" t="n">
         <v>-105.7629</v>
@@ -2062,7 +2062,7 @@
         <v>-32.2111</v>
       </c>
       <c r="I21" t="n">
-        <v>-73.55190000000002</v>
+        <v>-73.5519</v>
       </c>
       <c r="J21" t="n">
         <v>148.1958</v>
@@ -2089,16 +2089,16 @@
         <v>-475.6591</v>
       </c>
       <c r="R21" t="n">
-        <v>366.2669</v>
+        <v>366.2668999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4458</v>
+        <v>30.0422</v>
       </c>
       <c r="T21" t="n">
-        <v>3.0579</v>
+        <v>13.6488</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.504399999999999</v>
+        <v>16.3929</v>
       </c>
       <c r="V21" t="n">
         <v>-21.1033</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FRIVALCA LA MUELA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FRIVALCA LA MUELA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>30.8326</v>
+        <v>50.687</v>
       </c>
       <c r="E2" t="n">
-        <v>21.8144</v>
+        <v>50.687</v>
       </c>
       <c r="F2" t="n">
-        <v>9.0182</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>14.8126</v>
+        <v>50.687</v>
       </c>
       <c r="H2" t="n">
-        <v>7.523300000000001</v>
+        <v>27.0146</v>
       </c>
       <c r="I2" t="n">
-        <v>7.289599999999999</v>
+        <v>23.6727</v>
       </c>
       <c r="J2" t="n">
-        <v>42.2833</v>
+        <v>50.687</v>
       </c>
       <c r="K2" t="n">
-        <v>24.3164</v>
+        <v>27.0146</v>
       </c>
       <c r="L2" t="n">
-        <v>17.9668</v>
+        <v>23.6727</v>
       </c>
       <c r="M2" t="n">
-        <v>-27.4703</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.7931</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.6771</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-18.167</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-63.0961</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>44.9289</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>15.8522</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>5.836399999999999</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>10.0159</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>18.3343</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>36.7901</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-18.4557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>13.4542</v>
+        <v>30.8326</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9518</v>
+        <v>21.8144</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5025</v>
+        <v>9.0182</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.3798</v>
+        <v>14.8126</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.486999999999999</v>
+        <v>7.523300000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1068</v>
+        <v>7.289599999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1633</v>
+        <v>42.2833</v>
       </c>
       <c r="K3" t="n">
-        <v>3.855</v>
+        <v>24.3164</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3087</v>
+        <v>17.9668</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.543200000000001</v>
+        <v>-27.4703</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.341699999999999</v>
+        <v>-16.7931</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7982</v>
+        <v>-10.6771</v>
       </c>
       <c r="P3" t="n">
-        <v>6.446099999999999</v>
+        <v>-18.167</v>
       </c>
       <c r="Q3" t="n">
-        <v>-17.3853</v>
+        <v>-63.0961</v>
       </c>
       <c r="R3" t="n">
-        <v>23.8316</v>
+        <v>44.9289</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1401</v>
+        <v>15.8522</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1443</v>
+        <v>5.836399999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.004699999999999982</v>
+        <v>10.0159</v>
       </c>
       <c r="V3" t="n">
-        <v>6.2478</v>
+        <v>18.3343</v>
       </c>
       <c r="W3" t="n">
-        <v>10.0292</v>
+        <v>36.7901</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.7812</v>
+        <v>-18.4557</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6969</v>
+        <v>13.4542</v>
       </c>
       <c r="E4" t="n">
-        <v>6.227500000000001</v>
+        <v>1.9518</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5305000000000001</v>
+        <v>11.5025</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.6996</v>
+        <v>-2.3798</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2115000000000001</v>
+        <v>-5.486999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.4881</v>
+        <v>3.1068</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7782</v>
+        <v>6.1633</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2687</v>
+        <v>3.855</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4906999999999999</v>
+        <v>2.3087</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.4775</v>
+        <v>-8.543200000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.4801</v>
+        <v>-9.341699999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.9974</v>
+        <v>0.7982</v>
       </c>
       <c r="P4" t="n">
-        <v>5.0789</v>
+        <v>6.446099999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.985899999999999</v>
+        <v>-17.3853</v>
       </c>
       <c r="R4" t="n">
-        <v>14.0646</v>
+        <v>23.8316</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0318</v>
+        <v>3.1401</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1277</v>
+        <v>3.1443</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9040000000000001</v>
+        <v>-0.004699999999999982</v>
       </c>
       <c r="V4" t="n">
-        <v>5.285699999999999</v>
+        <v>6.2478</v>
       </c>
       <c r="W4" t="n">
-        <v>9.307099999999998</v>
+        <v>10.0292</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.0214</v>
+        <v>-3.7812</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ABAD CALAVIA</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,40 +796,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0494</v>
+        <v>6.426</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0205</v>
+        <v>6.426</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0494</v>
+        <v>6.426</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0494</v>
+        <v>4.605</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0205</v>
+        <v>6.426</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0205</v>
+        <v>4.605</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.821</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LAFUENTE</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1842</v>
+        <v>5.6969</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0205</v>
+        <v>6.227500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2047</v>
+        <v>-0.5305000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1842</v>
+        <v>-5.6996</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1842</v>
+        <v>-0.2115000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5.4881</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0205</v>
+        <v>5.7782</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>6.2687</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.4906999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2047</v>
+        <v>-11.4775</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2047</v>
+        <v>-6.4801</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-4.9974</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.0789</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-8.985899999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>14.0646</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.0318</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1277</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.9040000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.285699999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>9.307099999999998</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-4.0214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. SIMON RAMIS</t>
+          <t>D. ABAD CALAVIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.413</v>
+        <v>-0.0494</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0406</v>
+        <v>0.0205</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4535</v>
+        <v>-0.0698</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1998</v>
+        <v>-0.0494</v>
       </c>
       <c r="H7" t="n">
-        <v>0.065</v>
+        <v>-0.0494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1998</v>
+        <v>-0.0698</v>
       </c>
       <c r="N7" t="n">
-        <v>0.065</v>
+        <v>-0.0698</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,28 +1000,28 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0034</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.044</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. FERNANDEZ LAFUENTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.734900000000001</v>
+        <v>-0.1842</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.2098</v>
+        <v>0.0205</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4749</v>
+        <v>-0.2047</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6275999999999999</v>
+        <v>-0.1842</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0955</v>
+        <v>-0.1842</v>
       </c>
       <c r="I8" t="n">
-        <v>2.723</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4.135899999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1618</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9742000000000001</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5086</v>
+        <v>-0.2047</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.2572</v>
+        <v>-0.2047</v>
       </c>
       <c r="O8" t="n">
-        <v>1.7489</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5862999999999998</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.353</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>9.7669</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4824999999999999</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.117</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5995</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2939</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1098</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MILLS NALES</t>
+          <t>N. SIMON RAMIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.6313</v>
+        <v>-0.413</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.3043</v>
+        <v>0.0406</v>
       </c>
       <c r="F9" t="n">
-        <v>2.673</v>
+        <v>-0.4535</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9426</v>
+        <v>0.1998</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8392</v>
+        <v>0.065</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1034</v>
+        <v>0.1348</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.8521</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7499</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1022</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.1998</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0893</v>
+        <v>0.065</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0012</v>
+        <v>0.1348</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2311</v>
+        <v>-0.0034</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8459</v>
+        <v>0.0406</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6147</v>
+        <v>-0.044</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.5474</v>
+        <v>-2.734900000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8439999999999999</v>
+        <v>-5.2098</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.7035</v>
+        <v>2.4749</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5058</v>
+        <v>0.6275999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9878999999999993</v>
+        <v>-2.0955</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.4936</v>
+        <v>2.723</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3131</v>
+        <v>4.135899999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>9.7456</v>
+        <v>3.1618</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.4323</v>
+        <v>0.9742000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.8191</v>
+        <v>-3.5086</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.7576</v>
+        <v>-5.2572</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9385000000000001</v>
+        <v>1.7489</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5394</v>
+        <v>-0.5862999999999998</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.4695</v>
+        <v>-10.353</v>
       </c>
       <c r="R10" t="n">
-        <v>8.009</v>
+        <v>9.7669</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9319999999999997</v>
+        <v>-0.4824999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9768000000000001</v>
+        <v>1.117</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0450000000000001</v>
+        <v>-1.5995</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.5127</v>
+        <v>-2.2939</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>-0.1098</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.8486</v>
+        <v>-2.1842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>D. MILLS NALES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6003</v>
+        <v>-6.6313</v>
       </c>
       <c r="E11" t="n">
-        <v>2.250100000000001</v>
+        <v>-9.3043</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.8505</v>
+        <v>2.673</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.902400000000001</v>
+        <v>-3.9426</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4486</v>
+        <v>-1.8392</v>
       </c>
       <c r="I11" t="n">
-        <v>-12.3508</v>
+        <v>-2.1034</v>
       </c>
       <c r="J11" t="n">
-        <v>19.4796</v>
+        <v>-3.8521</v>
       </c>
       <c r="K11" t="n">
-        <v>19.6751</v>
+        <v>-1.7499</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1955000000000006</v>
+        <v>-2.1022</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.3819</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-13.2267</v>
+        <v>-0.0893</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.1554</v>
+        <v>-0.0012</v>
       </c>
       <c r="P11" t="n">
-        <v>5.0791</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q11" t="n">
-        <v>-26.3713</v>
+        <v>-4.8836</v>
       </c>
       <c r="R11" t="n">
-        <v>31.4503</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4572</v>
+        <v>-0.2311</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4402</v>
+        <v>-0.8459</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.8972</v>
+        <v>0.6147</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.319599999999999</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>7.701499999999999</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.0214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.7029</v>
+        <v>-7.5474</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.177</v>
+        <v>-0.8439999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.526</v>
+        <v>-6.7035</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.776300000000001</v>
+        <v>-3.5058</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.9673</v>
+        <v>0.9878999999999993</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.809</v>
+        <v>-4.4936</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3964</v>
+        <v>4.3131</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.52</v>
+        <v>9.7456</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9165</v>
+        <v>-5.4323</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.1726</v>
+        <v>-7.8191</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4472</v>
+        <v>-8.7576</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.7254</v>
+        <v>0.9385000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3674</v>
+        <v>2.5394</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.3764</v>
+        <v>-5.4695</v>
       </c>
       <c r="R12" t="n">
-        <v>8.008900000000001</v>
+        <v>8.009</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2351</v>
+        <v>0.9319999999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2484</v>
+        <v>0.9768000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.01319999999999999</v>
+        <v>-0.0450000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7944</v>
+        <v>-7.5127</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5544</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3489</v>
+        <v>-6.8486</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.9786</v>
+        <v>-7.6003</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.2917</v>
+        <v>2.250100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6864999999999998</v>
+        <v>-9.8505</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.1539</v>
+        <v>-5.902400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5932</v>
+        <v>6.4486</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.5605</v>
+        <v>-12.3508</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1602</v>
+        <v>19.4796</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5874</v>
+        <v>19.6751</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.7477</v>
+        <v>-0.1955000000000006</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.9935</v>
+        <v>-25.3819</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.1805</v>
+        <v>-13.2267</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8127999999999999</v>
+        <v>-12.1554</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.2975</v>
+        <v>5.0791</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6973</v>
+        <v>-26.3713</v>
       </c>
       <c r="R13" t="n">
-        <v>8.399800000000001</v>
+        <v>31.4503</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.355</v>
+        <v>-1.4572</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3472999999999999</v>
+        <v>1.4402</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7023000000000001</v>
+        <v>-2.8972</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1722</v>
+        <v>-5.319599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>7.701499999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3908</v>
+        <v>-13.0214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.1823</v>
+        <v>-9.7029</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.2495</v>
+        <v>-8.177</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9330000000000003</v>
+        <v>-1.526</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.1394</v>
+        <v>-6.776300000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7744</v>
+        <v>-4.9673</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.3648</v>
+        <v>-1.809</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.229799999999999</v>
+        <v>0.3964</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6239000000000002</v>
+        <v>-2.52</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.8538</v>
+        <v>2.9165</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.9098</v>
+        <v>-7.1726</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3987</v>
+        <v>-2.4472</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.5111</v>
+        <v>-4.7254</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.2741</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.4553</v>
+        <v>-9.3764</v>
       </c>
       <c r="R14" t="n">
-        <v>9.181100000000001</v>
+        <v>8.008900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3541</v>
+        <v>0.2351</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8266</v>
+        <v>0.2484</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5274000000000001</v>
+        <v>-0.01319999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.1225</v>
+        <v>-1.7944</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>0.5544</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.7318</v>
+        <v>-2.3489</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.4557</v>
+        <v>-12.9786</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.3772</v>
+        <v>-12.2917</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0781</v>
+        <v>-0.6864999999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.648</v>
+        <v>-6.1539</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0626</v>
+        <v>-2.5932</v>
       </c>
       <c r="I15" t="n">
-        <v>-19.7107</v>
+        <v>-3.5605</v>
       </c>
       <c r="J15" t="n">
-        <v>15.3213</v>
+        <v>-1.1602</v>
       </c>
       <c r="K15" t="n">
-        <v>24.7588</v>
+        <v>1.5874</v>
       </c>
       <c r="L15" t="n">
-        <v>-9.4374</v>
+        <v>-2.7477</v>
       </c>
       <c r="M15" t="n">
-        <v>-33.9693</v>
+        <v>-4.9935</v>
       </c>
       <c r="N15" t="n">
-        <v>-23.6962</v>
+        <v>-4.1805</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.2733</v>
+        <v>-0.8127999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-37.3105</v>
+        <v>-4.2975</v>
       </c>
       <c r="Q15" t="n">
-        <v>-79.89530000000001</v>
+        <v>-12.6973</v>
       </c>
       <c r="R15" t="n">
-        <v>42.5849</v>
+        <v>8.399800000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>4.9504</v>
+        <v>-0.355</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9682999999999998</v>
+        <v>0.3472999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>3.9825</v>
+        <v>-0.7023000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>24.5522</v>
+        <v>-2.1722</v>
       </c>
       <c r="W15" t="n">
-        <v>38.2282</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.6759</v>
+        <v>-3.3908</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.4541</v>
+        <v>-22.1823</v>
       </c>
       <c r="E16" t="n">
-        <v>-28.812</v>
+        <v>-21.2495</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3581</v>
+        <v>-0.9330000000000003</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.6708</v>
+        <v>-15.1394</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.588000000000001</v>
+        <v>-1.7744</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.083200000000001</v>
+        <v>-13.3648</v>
       </c>
       <c r="J16" t="n">
-        <v>4.004700000000001</v>
+        <v>-9.229799999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>5.949000000000001</v>
+        <v>0.6239000000000002</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9442</v>
+        <v>-9.8538</v>
       </c>
       <c r="M16" t="n">
-        <v>-14.6757</v>
+        <v>-5.9098</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.536799999999999</v>
+        <v>-2.3987</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.1389</v>
+        <v>-3.5111</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.618399999999999</v>
+        <v>-5.2741</v>
       </c>
       <c r="Q16" t="n">
-        <v>-38.2869</v>
+        <v>-14.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>30.6687</v>
+        <v>9.181100000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5929</v>
+        <v>2.3541</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9056999999999999</v>
+        <v>1.8266</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4989</v>
+        <v>0.5274000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-10.7575</v>
+        <v>-4.1225</v>
       </c>
       <c r="W16" t="n">
-        <v>6.3764</v>
+        <v>0.6093</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.1339</v>
+        <v>-4.7318</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-28.7512</v>
+        <v>-26.4557</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.280800000000001</v>
+        <v>-25.3772</v>
       </c>
       <c r="F17" t="n">
-        <v>-19.4705</v>
+        <v>-1.0781</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.6175</v>
+        <v>-18.648</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7499000000000007</v>
+        <v>1.0626</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.867599999999999</v>
+        <v>-19.7107</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7067</v>
+        <v>15.3213</v>
       </c>
       <c r="K17" t="n">
-        <v>13.6578</v>
+        <v>24.7588</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0488</v>
+        <v>-9.4374</v>
       </c>
       <c r="M17" t="n">
-        <v>-23.3243</v>
+        <v>-33.9693</v>
       </c>
       <c r="N17" t="n">
-        <v>-14.4076</v>
+        <v>-23.6962</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.916399999999999</v>
+        <v>-10.2733</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.2511</v>
+        <v>-37.3105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-31.4499</v>
+        <v>-79.89530000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>25.199</v>
+        <v>42.5849</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4727</v>
+        <v>4.9504</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9163</v>
+        <v>0.9682999999999998</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5561</v>
+        <v>3.9825</v>
       </c>
       <c r="V17" t="n">
-        <v>-19.3553</v>
+        <v>24.5522</v>
       </c>
       <c r="W17" t="n">
-        <v>3.545999999999999</v>
+        <v>38.2282</v>
       </c>
       <c r="X17" t="n">
-        <v>-22.9014</v>
+        <v>-13.6759</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.4624</v>
+        <v>-28.7512</v>
       </c>
       <c r="E18" t="n">
-        <v>-22.4398</v>
+        <v>-9.280800000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.022399999999999</v>
+        <v>-19.4705</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.1342</v>
+        <v>-6.6175</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.7415</v>
+        <v>-0.7499000000000007</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.3925</v>
+        <v>-5.867599999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7809</v>
+        <v>16.7067</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2325</v>
+        <v>13.6578</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.013299999999999</v>
+        <v>3.0488</v>
       </c>
       <c r="M18" t="n">
-        <v>-10.353</v>
+        <v>-23.3243</v>
       </c>
       <c r="N18" t="n">
-        <v>-6.974</v>
+        <v>-14.4076</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.3792</v>
+        <v>-8.916399999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-9.181100000000001</v>
+        <v>-6.2511</v>
       </c>
       <c r="Q18" t="n">
-        <v>-24.2224</v>
+        <v>-31.4499</v>
       </c>
       <c r="R18" t="n">
-        <v>15.0413</v>
+        <v>25.199</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7758999999999998</v>
+        <v>3.4727</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.369</v>
+        <v>1.9163</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5931</v>
+        <v>1.5561</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.3712</v>
+        <v>-19.3553</v>
       </c>
       <c r="W18" t="n">
-        <v>4.9323</v>
+        <v>3.545999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.3036</v>
+        <v>-22.9014</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-33.9571</v>
+        <v>-31.4624</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.6799</v>
+        <v>-22.4398</v>
       </c>
       <c r="F19" t="n">
-        <v>-14.2771</v>
+        <v>-9.022399999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.7877</v>
+        <v>-12.1342</v>
       </c>
       <c r="H19" t="n">
-        <v>-15.8163</v>
+        <v>-6.7415</v>
       </c>
       <c r="I19" t="n">
-        <v>-13.9717</v>
+        <v>-5.3925</v>
       </c>
       <c r="J19" t="n">
-        <v>8.1722</v>
+        <v>-1.7809</v>
       </c>
       <c r="K19" t="n">
-        <v>9.172800000000001</v>
+        <v>0.2325</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.000800000000001</v>
+        <v>-2.013299999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-37.9603</v>
+        <v>-10.353</v>
       </c>
       <c r="N19" t="n">
-        <v>-24.989</v>
+        <v>-6.974</v>
       </c>
       <c r="O19" t="n">
-        <v>-12.9711</v>
+        <v>-3.3792</v>
       </c>
       <c r="P19" t="n">
-        <v>-8.399699999999999</v>
+        <v>-9.181100000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-52.938</v>
+        <v>-24.2224</v>
       </c>
       <c r="R19" t="n">
-        <v>44.5381</v>
+        <v>15.0413</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4300000000000003</v>
+        <v>-0.7758999999999998</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2106999999999999</v>
+        <v>-1.369</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6408999999999997</v>
+        <v>0.5931</v>
       </c>
       <c r="V19" t="n">
-        <v>4.660699999999999</v>
+        <v>-9.3712</v>
       </c>
       <c r="W19" t="n">
-        <v>24.8748</v>
+        <v>4.9323</v>
       </c>
       <c r="X19" t="n">
-        <v>-20.2145</v>
+        <v>-14.3036</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-38.0958</v>
+        <v>-33.8797</v>
       </c>
       <c r="E20" t="n">
-        <v>-36.5746</v>
+        <v>-35.2378</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.521</v>
+        <v>1.3581</v>
       </c>
       <c r="G20" t="n">
-        <v>6.188700000000001</v>
+        <v>-17.0968</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.201100000000001</v>
+        <v>-8.1929</v>
       </c>
       <c r="I20" t="n">
-        <v>8.389799999999999</v>
+        <v>-8.9041</v>
       </c>
       <c r="J20" t="n">
-        <v>37.4231</v>
+        <v>-2.421199999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>20.5126</v>
+        <v>1.3442</v>
       </c>
       <c r="L20" t="n">
-        <v>16.9108</v>
+        <v>-3.7652</v>
       </c>
       <c r="M20" t="n">
-        <v>-31.2345</v>
+        <v>-14.6757</v>
       </c>
       <c r="N20" t="n">
-        <v>-22.7136</v>
+        <v>-9.536799999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.520900000000001</v>
+        <v>-5.1389</v>
       </c>
       <c r="P20" t="n">
-        <v>-27.348</v>
+        <v>-7.618399999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-75.7929</v>
+        <v>-38.2869</v>
       </c>
       <c r="R20" t="n">
-        <v>48.445</v>
+        <v>30.6687</v>
       </c>
       <c r="S20" t="n">
-        <v>0.216</v>
+        <v>1.5929</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4312</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6471</v>
+        <v>2.4989</v>
       </c>
       <c r="V20" t="n">
-        <v>-17.1526</v>
+        <v>-10.7575</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2258</v>
+        <v>6.3764</v>
       </c>
       <c r="X20" t="n">
-        <v>-20.3782</v>
+        <v>-17.1339</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,66 +2047,222 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-206.2169</v>
+        <v>-33.9571</v>
       </c>
       <c r="E21" t="n">
-        <v>-166.9152</v>
+        <v>-19.6799</v>
       </c>
       <c r="F21" t="n">
+        <v>-14.2771</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-29.7877</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-15.8163</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-13.9717</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.1722</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9.172800000000001</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.000800000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-37.9603</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-24.989</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-12.9711</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-8.399699999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-52.938</v>
+      </c>
+      <c r="R21" t="n">
+        <v>44.5381</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.4300000000000003</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.2106999999999999</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6408999999999997</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.660699999999999</v>
+      </c>
+      <c r="W21" t="n">
+        <v>24.8748</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-20.2145</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P. CABANERO PUERTAS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-88.78279999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-87.2617</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.521</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-44.4986</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-29.2159</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-15.2825</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-13.264</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-6.5021</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-6.7615</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-31.2345</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-22.7136</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-8.520900000000001</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-27.348</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-75.7929</v>
+      </c>
+      <c r="R22" t="n">
+        <v>48.445</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1.4312</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.6471</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-17.1526</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.2258</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-20.3782</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-206.2165</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-166.9151</v>
+      </c>
+      <c r="F23" t="n">
         <v>-39.3004</v>
       </c>
-      <c r="G21" t="n">
-        <v>-105.7629</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-32.2111</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-73.5519</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="G23" t="n">
+        <v>-105.7632</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-32.2112</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-73.5514</v>
+      </c>
+      <c r="J23" t="n">
         <v>148.1958</v>
       </c>
-      <c r="K21" t="n">
-        <v>139.2885</v>
-      </c>
-      <c r="L21" t="n">
-        <v>8.907899999999998</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="K23" t="n">
+        <v>139.2886</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8.908299999999999</v>
+      </c>
+      <c r="M23" t="n">
         <v>-253.9587</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N23" t="n">
         <v>-171.4988</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>-82.45979999999999</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P23" t="n">
         <v>-109.3924</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q23" t="n">
         <v>-475.6591</v>
       </c>
-      <c r="R21" t="n">
-        <v>366.2668999999999</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R23" t="n">
+        <v>366.2669</v>
+      </c>
+      <c r="S23" t="n">
         <v>30.0422</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>13.6488</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>16.3929</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V23" t="n">
         <v>-21.1033</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W23" t="n">
         <v>146.8969</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-168.0008</v>
       </c>
     </row>
